--- a/main/ig/StructureDefinition-fr-patient-ins-document.xlsx
+++ b/main/ig/StructureDefinition-fr-patient-ins-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:20:55+00:00</t>
+    <t>2025-05-23T08:30:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-patient-ins-document.xlsx
+++ b/main/ig/StructureDefinition-fr-patient-ins-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-23T08:30:51+00:00</t>
+    <t>2025-05-23T15:44:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-patient-ins-document.xlsx
+++ b/main/ig/StructureDefinition-fr-patient-ins-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-23T15:44:19+00:00</t>
+    <t>2025-08-01T08:11:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-patient-ins-document.xlsx
+++ b/main/ig/StructureDefinition-fr-patient-ins-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-01T08:11:50+00:00</t>
+    <t>2025-08-22T10:16:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-patient-ins-document.xlsx
+++ b/main/ig/StructureDefinition-fr-patient-ins-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-22T10:16:53+00:00</t>
+    <t>2025-08-25T15:42:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-patient-ins-document.xlsx
+++ b/main/ig/StructureDefinition-fr-patient-ins-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-25T15:42:10+00:00</t>
+    <t>2025-10-02T14:05:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -5610,7 +5610,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
         <v>219</v>
       </c>
@@ -13225,7 +13225,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="88" hidden="true">
+    <row r="88">
       <c r="A88" t="s" s="2">
         <v>482</v>
       </c>
@@ -16396,7 +16396,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="115" hidden="true">
+    <row r="115">
       <c r="A115" t="s" s="2">
         <v>523</v>
       </c>
@@ -18863,7 +18863,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="136" hidden="true">
+    <row r="136">
       <c r="A136" t="s" s="2">
         <v>622</v>
       </c>
@@ -19214,7 +19214,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="139" hidden="true">
+    <row r="139">
       <c r="A139" t="s" s="2">
         <v>628</v>
       </c>
@@ -20269,7 +20269,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="148" hidden="true">
+    <row r="148">
       <c r="A148" t="s" s="2">
         <v>651</v>
       </c>
@@ -20386,7 +20386,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="149" hidden="true">
+    <row r="149">
       <c r="A149" t="s" s="2">
         <v>660</v>
       </c>
@@ -24497,12 +24497,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AO183">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>

--- a/main/ig/StructureDefinition-fr-patient-ins-document.xlsx
+++ b/main/ig/StructureDefinition-fr-patient-ins-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-02T14:05:03+00:00</t>
+    <t>2025-10-02T15:16:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-patient-ins-document.xlsx
+++ b/main/ig/StructureDefinition-fr-patient-ins-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-02T15:16:38+00:00</t>
+    <t>2025-10-13T15:21:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-patient-ins-document.xlsx
+++ b/main/ig/StructureDefinition-fr-patient-ins-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-13T15:21:05+00:00</t>
+    <t>2025-10-20T17:15:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-patient-ins-document.xlsx
+++ b/main/ig/StructureDefinition-fr-patient-ins-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-20T17:15:49+00:00</t>
+    <t>2025-10-21T08:14:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-patient-ins-document.xlsx
+++ b/main/ig/StructureDefinition-fr-patient-ins-document.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6832" uniqueCount="843">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6832" uniqueCount="841">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-21T08:14:34+00:00</t>
+    <t>2025-10-21T15:23:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1876,7 +1876,7 @@
 </t>
   </si>
   <si>
-    <t>Nom utilisé</t>
+    <t>Family name (often called 'Surname')</t>
   </si>
   <si>
     <t>The part of a name that links to the genealogy. In some cultures (e.g. Eritrea) the family name of a son is the first name of his father.</t>
@@ -1904,7 +1904,7 @@
 middle name</t>
   </si>
   <si>
-    <t>Prénom utilisé</t>
+    <t>Given names (not always 'first'). Includes middle names</t>
   </si>
   <si>
     <t>Given name.</t>
@@ -2013,7 +2013,7 @@
 </t>
   </si>
   <si>
-    <t>Liste des prénoms de l'acte de naissance</t>
+    <t>Dans le cas d’une identité créée ou modifiée par un appel au téléservice INSi, il s’agit de la liste des prénoms retournée par le téléservice. Ce composant contient tous les prénoms du patient, y compris le premier, que l'on retrouve également dans le champ name.given. Il s'agit de la liste des prénoms du patient, qu'elle soit issue d'une saisie locale ou du retour à l'appel au téléservice INSi. Conformément aux spécifications INS, cette liste est constituée des prénoms, séparés par des espaces.</t>
   </si>
   <si>
     <t>Prénoms de l'acte de naissance</t>
@@ -2028,13 +2028,10 @@
     <t>Patient.name:officialName.family</t>
   </si>
   <si>
-    <t>Nom de naissance</t>
-  </si>
-  <si>
     <t>Patient.name:officialName.given</t>
   </si>
   <si>
-    <t>Premier prénom de l'acte de naissance</t>
+    <t>Dans le cas d’une identité créée ou modifiée par un appel au téléservice INSi, il est nécessaire d’extraire le premier prénom de la liste des prénoms retournée par le téléservice et de l'inclure dans le champs given. En cas de prénom composé, given peut par exemple contenir 'Anne-sophie' ou 'Anne Sophie'.</t>
   </si>
   <si>
     <t>Patient.name:officialName.prefix</t>
@@ -2580,10 +2577,6 @@
     <t>This may be the primary care provider (in a GP context), or it may be a patient nominated care manager in a community/disability setting, or even organization that will provide people to perform the care provider roles.  It is not to be used to record Care Teams, these should be in a CareTeam resource that may be linked to the CarePlan or EpisodeOfCare resources.
 Multiple GPs may be recorded against the patient for various reasons, such as a student that has his home GP listed along with the GP at university during the school semesters, or a "fly-in/fly-out" worker that has the onsite GP also included with his home GP to remain aware of medical issues.
 Jurisdictions may decide that they can profile this down to 1 if desired, or 1 per type.</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-pat-gp-1:Le generalPractitioner doit être un PractitionerRole contenant un code[typeCode] fixé à 'INF'. {resolve().code.coding.where(code='INF').exists()}pat-gp-2:Le generalPractitioner doit être un PractitionerRole contenant un code[functionCode] fixé à 'PCP'. {resolve().code.coding.where(code='PCP').exists()}pat-gp-3:Le generalPractitioner doit être un PractitionerRole contenant un code[classCode] fixé à 'PROV'. {resolve().code.coding.where(code='PROV').exists()}</t>
   </si>
   <si>
     <t>subjectOf.CareEvent.performer.AssignedEntity</t>
@@ -18415,7 +18408,7 @@
         <v>79</v>
       </c>
       <c r="G132" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H132" t="s" s="2">
         <v>81</v>
@@ -19600,7 +19593,7 @@
         <v>103</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>636</v>
+        <v>586</v>
       </c>
       <c r="M142" t="s" s="2">
         <v>587</v>
@@ -19688,7 +19681,7 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B143" t="s" s="2">
         <v>593</v>
@@ -19717,7 +19710,7 @@
         <v>103</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="M143" t="s" s="2">
         <v>596</v>
@@ -19805,7 +19798,7 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B144" t="s" s="2">
         <v>602</v>
@@ -19920,7 +19913,7 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B145" t="s" s="2">
         <v>609</v>
@@ -20035,7 +20028,7 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B146" t="s" s="2">
         <v>616</v>
@@ -20152,10 +20145,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -20178,19 +20171,19 @@
         <v>81</v>
       </c>
       <c r="K147" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="L147" t="s" s="2">
         <v>643</v>
       </c>
-      <c r="L147" t="s" s="2">
+      <c r="M147" t="s" s="2">
         <v>644</v>
       </c>
-      <c r="M147" t="s" s="2">
+      <c r="N147" t="s" s="2">
         <v>645</v>
       </c>
-      <c r="N147" t="s" s="2">
+      <c r="O147" t="s" s="2">
         <v>646</v>
-      </c>
-      <c r="O147" t="s" s="2">
-        <v>647</v>
       </c>
       <c r="P147" t="s" s="2">
         <v>81</v>
@@ -20239,7 +20232,7 @@
         <v>81</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>79</v>
@@ -20251,19 +20244,19 @@
         <v>204</v>
       </c>
       <c r="AJ147" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="AK147" t="s" s="2">
         <v>648</v>
       </c>
-      <c r="AK147" t="s" s="2">
+      <c r="AL147" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM147" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN147" t="s" s="2">
         <v>649</v>
-      </c>
-      <c r="AL147" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM147" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN147" t="s" s="2">
-        <v>650</v>
       </c>
       <c r="AO147" t="s" s="2">
         <v>81</v>
@@ -20271,10 +20264,10 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20300,16 +20293,16 @@
         <v>170</v>
       </c>
       <c r="L148" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="M148" t="s" s="2">
         <v>652</v>
       </c>
-      <c r="M148" t="s" s="2">
+      <c r="N148" t="s" s="2">
         <v>653</v>
       </c>
-      <c r="N148" t="s" s="2">
+      <c r="O148" t="s" s="2">
         <v>654</v>
-      </c>
-      <c r="O148" t="s" s="2">
-        <v>655</v>
       </c>
       <c r="P148" t="s" s="2">
         <v>81</v>
@@ -20338,7 +20331,7 @@
       </c>
       <c r="Y148" s="2"/>
       <c r="Z148" t="s" s="2">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="AA148" t="s" s="2">
         <v>81</v>
@@ -20356,7 +20349,7 @@
         <v>81</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>79</v>
@@ -20371,16 +20364,16 @@
         <v>101</v>
       </c>
       <c r="AK148" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="AL148" t="s" s="2">
         <v>657</v>
       </c>
-      <c r="AL148" t="s" s="2">
+      <c r="AM148" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN148" t="s" s="2">
         <v>658</v>
-      </c>
-      <c r="AM148" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN148" t="s" s="2">
-        <v>659</v>
       </c>
       <c r="AO148" t="s" s="2">
         <v>81</v>
@@ -20388,10 +20381,10 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20414,19 +20407,19 @@
         <v>90</v>
       </c>
       <c r="K149" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="L149" t="s" s="2">
         <v>661</v>
       </c>
-      <c r="L149" t="s" s="2">
+      <c r="M149" t="s" s="2">
         <v>662</v>
       </c>
-      <c r="M149" t="s" s="2">
+      <c r="N149" t="s" s="2">
         <v>663</v>
       </c>
-      <c r="N149" t="s" s="2">
+      <c r="O149" t="s" s="2">
         <v>664</v>
-      </c>
-      <c r="O149" t="s" s="2">
-        <v>665</v>
       </c>
       <c r="P149" t="s" s="2">
         <v>81</v>
@@ -20475,7 +20468,7 @@
         <v>81</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>79</v>
@@ -20490,27 +20483,27 @@
         <v>101</v>
       </c>
       <c r="AK149" t="s" s="2">
+        <v>665</v>
+      </c>
+      <c r="AL149" t="s" s="2">
         <v>666</v>
       </c>
-      <c r="AL149" t="s" s="2">
+      <c r="AM149" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN149" t="s" s="2">
         <v>667</v>
       </c>
-      <c r="AM149" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN149" t="s" s="2">
+      <c r="AO149" t="s" s="2">
         <v>668</v>
-      </c>
-      <c r="AO149" t="s" s="2">
-        <v>669</v>
       </c>
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20533,19 +20526,19 @@
         <v>90</v>
       </c>
       <c r="K150" t="s" s="2">
+        <v>670</v>
+      </c>
+      <c r="L150" t="s" s="2">
         <v>671</v>
       </c>
-      <c r="L150" t="s" s="2">
+      <c r="M150" t="s" s="2">
         <v>672</v>
       </c>
-      <c r="M150" t="s" s="2">
+      <c r="N150" t="s" s="2">
         <v>673</v>
       </c>
-      <c r="N150" t="s" s="2">
+      <c r="O150" t="s" s="2">
         <v>674</v>
-      </c>
-      <c r="O150" t="s" s="2">
-        <v>675</v>
       </c>
       <c r="P150" t="s" s="2">
         <v>81</v>
@@ -20594,7 +20587,7 @@
         <v>81</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>79</v>
@@ -20609,7 +20602,7 @@
         <v>101</v>
       </c>
       <c r="AK150" t="s" s="2">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="AL150" t="s" s="2">
         <v>107</v>
@@ -20618,7 +20611,7 @@
         <v>81</v>
       </c>
       <c r="AN150" t="s" s="2">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="AO150" t="s" s="2">
         <v>81</v>
@@ -20626,10 +20619,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20664,7 +20657,7 @@
         <v>240</v>
       </c>
       <c r="O151" t="s" s="2">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="P151" t="s" s="2">
         <v>81</v>
@@ -20713,7 +20706,7 @@
         <v>81</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>79</v>
@@ -20745,10 +20738,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -20774,14 +20767,14 @@
         <v>384</v>
       </c>
       <c r="L152" t="s" s="2">
+        <v>680</v>
+      </c>
+      <c r="M152" t="s" s="2">
         <v>681</v>
-      </c>
-      <c r="M152" t="s" s="2">
-        <v>682</v>
       </c>
       <c r="N152" s="2"/>
       <c r="O152" t="s" s="2">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="P152" t="s" s="2">
         <v>81</v>
@@ -20810,7 +20803,7 @@
       </c>
       <c r="Y152" s="2"/>
       <c r="Z152" t="s" s="2">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="AA152" t="s" s="2">
         <v>81</v>
@@ -20828,7 +20821,7 @@
         <v>81</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>79</v>
@@ -20843,16 +20836,16 @@
         <v>101</v>
       </c>
       <c r="AK152" t="s" s="2">
+        <v>684</v>
+      </c>
+      <c r="AL152" t="s" s="2">
         <v>685</v>
       </c>
-      <c r="AL152" t="s" s="2">
+      <c r="AM152" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN152" t="s" s="2">
         <v>686</v>
-      </c>
-      <c r="AM152" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN152" t="s" s="2">
-        <v>687</v>
       </c>
       <c r="AO152" t="s" s="2">
         <v>81</v>
@@ -20860,10 +20853,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -20886,19 +20879,19 @@
         <v>81</v>
       </c>
       <c r="K153" t="s" s="2">
+        <v>688</v>
+      </c>
+      <c r="L153" t="s" s="2">
         <v>689</v>
       </c>
-      <c r="L153" t="s" s="2">
+      <c r="M153" t="s" s="2">
         <v>690</v>
       </c>
-      <c r="M153" t="s" s="2">
+      <c r="N153" t="s" s="2">
         <v>691</v>
       </c>
-      <c r="N153" t="s" s="2">
+      <c r="O153" t="s" s="2">
         <v>692</v>
-      </c>
-      <c r="O153" t="s" s="2">
-        <v>693</v>
       </c>
       <c r="P153" t="s" s="2">
         <v>81</v>
@@ -20947,7 +20940,7 @@
         <v>81</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>79</v>
@@ -20962,7 +20955,7 @@
         <v>101</v>
       </c>
       <c r="AK153" t="s" s="2">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="AL153" t="s" s="2">
         <v>107</v>
@@ -20971,7 +20964,7 @@
         <v>81</v>
       </c>
       <c r="AN153" t="s" s="2">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="AO153" t="s" s="2">
         <v>81</v>
@@ -20979,10 +20972,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -21005,19 +20998,19 @@
         <v>81</v>
       </c>
       <c r="K154" t="s" s="2">
+        <v>696</v>
+      </c>
+      <c r="L154" t="s" s="2">
         <v>697</v>
       </c>
-      <c r="L154" t="s" s="2">
+      <c r="M154" t="s" s="2">
         <v>698</v>
       </c>
-      <c r="M154" t="s" s="2">
+      <c r="N154" t="s" s="2">
         <v>699</v>
       </c>
-      <c r="N154" t="s" s="2">
+      <c r="O154" t="s" s="2">
         <v>700</v>
-      </c>
-      <c r="O154" t="s" s="2">
-        <v>701</v>
       </c>
       <c r="P154" t="s" s="2">
         <v>81</v>
@@ -21066,7 +21059,7 @@
         <v>81</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>79</v>
@@ -21081,7 +21074,7 @@
         <v>101</v>
       </c>
       <c r="AK154" t="s" s="2">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="AL154" t="s" s="2">
         <v>107</v>
@@ -21090,7 +21083,7 @@
         <v>81</v>
       </c>
       <c r="AN154" t="s" s="2">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="AO154" t="s" s="2">
         <v>81</v>
@@ -21098,10 +21091,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -21124,19 +21117,19 @@
         <v>81</v>
       </c>
       <c r="K155" t="s" s="2">
+        <v>704</v>
+      </c>
+      <c r="L155" t="s" s="2">
         <v>705</v>
       </c>
-      <c r="L155" t="s" s="2">
+      <c r="M155" t="s" s="2">
         <v>706</v>
       </c>
-      <c r="M155" t="s" s="2">
+      <c r="N155" t="s" s="2">
         <v>707</v>
       </c>
-      <c r="N155" t="s" s="2">
+      <c r="O155" t="s" s="2">
         <v>708</v>
-      </c>
-      <c r="O155" t="s" s="2">
-        <v>709</v>
       </c>
       <c r="P155" t="s" s="2">
         <v>81</v>
@@ -21185,7 +21178,7 @@
         <v>81</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>79</v>
@@ -21197,10 +21190,10 @@
         <v>81</v>
       </c>
       <c r="AJ155" t="s" s="2">
+        <v>709</v>
+      </c>
+      <c r="AK155" t="s" s="2">
         <v>710</v>
-      </c>
-      <c r="AK155" t="s" s="2">
-        <v>711</v>
       </c>
       <c r="AL155" t="s" s="2">
         <v>107</v>
@@ -21217,10 +21210,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21332,10 +21325,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21445,13 +21438,13 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
+        <v>713</v>
+      </c>
+      <c r="B158" t="s" s="2">
+        <v>712</v>
+      </c>
+      <c r="C158" t="s" s="2">
         <v>714</v>
-      </c>
-      <c r="B158" t="s" s="2">
-        <v>713</v>
-      </c>
-      <c r="C158" t="s" s="2">
-        <v>715</v>
       </c>
       <c r="D158" t="s" s="2">
         <v>81</v>
@@ -21473,13 +21466,13 @@
         <v>81</v>
       </c>
       <c r="K158" t="s" s="2">
+        <v>715</v>
+      </c>
+      <c r="L158" t="s" s="2">
         <v>716</v>
       </c>
-      <c r="L158" t="s" s="2">
+      <c r="M158" t="s" s="2">
         <v>717</v>
-      </c>
-      <c r="M158" t="s" s="2">
-        <v>718</v>
       </c>
       <c r="N158" s="2"/>
       <c r="O158" s="2"/>
@@ -21562,13 +21555,13 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
+        <v>718</v>
+      </c>
+      <c r="B159" t="s" s="2">
+        <v>712</v>
+      </c>
+      <c r="C159" t="s" s="2">
         <v>719</v>
-      </c>
-      <c r="B159" t="s" s="2">
-        <v>713</v>
-      </c>
-      <c r="C159" t="s" s="2">
-        <v>720</v>
       </c>
       <c r="D159" t="s" s="2">
         <v>81</v>
@@ -21590,13 +21583,13 @@
         <v>81</v>
       </c>
       <c r="K159" t="s" s="2">
+        <v>720</v>
+      </c>
+      <c r="L159" t="s" s="2">
         <v>721</v>
       </c>
-      <c r="L159" t="s" s="2">
+      <c r="M159" t="s" s="2">
         <v>722</v>
-      </c>
-      <c r="M159" t="s" s="2">
-        <v>723</v>
       </c>
       <c r="N159" s="2"/>
       <c r="O159" s="2"/>
@@ -21679,14 +21672,14 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E160" s="2"/>
       <c r="F160" t="s" s="2">
@@ -21708,10 +21701,10 @@
         <v>110</v>
       </c>
       <c r="L160" t="s" s="2">
+        <v>725</v>
+      </c>
+      <c r="M160" t="s" s="2">
         <v>726</v>
-      </c>
-      <c r="M160" t="s" s="2">
-        <v>727</v>
       </c>
       <c r="N160" t="s" s="2">
         <v>113</v>
@@ -21766,7 +21759,7 @@
         <v>81</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>79</v>
@@ -21798,10 +21791,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -21827,14 +21820,14 @@
         <v>384</v>
       </c>
       <c r="L161" t="s" s="2">
+        <v>729</v>
+      </c>
+      <c r="M161" t="s" s="2">
         <v>730</v>
-      </c>
-      <c r="M161" t="s" s="2">
-        <v>731</v>
       </c>
       <c r="N161" s="2"/>
       <c r="O161" t="s" s="2">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="P161" t="s" s="2">
         <v>81</v>
@@ -21862,16 +21855,16 @@
         <v>152</v>
       </c>
       <c r="Y161" t="s" s="2">
+        <v>732</v>
+      </c>
+      <c r="Z161" t="s" s="2">
         <v>733</v>
       </c>
-      <c r="Z161" t="s" s="2">
+      <c r="AA161" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB161" t="s" s="2">
         <v>734</v>
-      </c>
-      <c r="AA161" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB161" t="s" s="2">
-        <v>735</v>
       </c>
       <c r="AC161" s="2"/>
       <c r="AD161" t="s" s="2">
@@ -21881,7 +21874,7 @@
         <v>116</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>79</v>
@@ -21896,7 +21889,7 @@
         <v>101</v>
       </c>
       <c r="AK161" t="s" s="2">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="AL161" t="s" s="2">
         <v>107</v>
@@ -21905,7 +21898,7 @@
         <v>81</v>
       </c>
       <c r="AN161" t="s" s="2">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="AO161" t="s" s="2">
         <v>81</v>
@@ -21913,13 +21906,13 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
+        <v>737</v>
+      </c>
+      <c r="B162" t="s" s="2">
+        <v>728</v>
+      </c>
+      <c r="C162" t="s" s="2">
         <v>738</v>
-      </c>
-      <c r="B162" t="s" s="2">
-        <v>729</v>
-      </c>
-      <c r="C162" t="s" s="2">
-        <v>739</v>
       </c>
       <c r="D162" t="s" s="2">
         <v>81</v>
@@ -21944,14 +21937,14 @@
         <v>384</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="N162" s="2"/>
       <c r="O162" t="s" s="2">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="P162" t="s" s="2">
         <v>81</v>
@@ -21980,7 +21973,7 @@
       </c>
       <c r="Y162" s="2"/>
       <c r="Z162" t="s" s="2">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="AA162" t="s" s="2">
         <v>81</v>
@@ -21998,7 +21991,7 @@
         <v>81</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>79</v>
@@ -22013,7 +22006,7 @@
         <v>101</v>
       </c>
       <c r="AK162" t="s" s="2">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="AL162" t="s" s="2">
         <v>107</v>
@@ -22022,7 +22015,7 @@
         <v>81</v>
       </c>
       <c r="AN162" t="s" s="2">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="AO162" t="s" s="2">
         <v>81</v>
@@ -22030,13 +22023,13 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
+        <v>741</v>
+      </c>
+      <c r="B163" t="s" s="2">
+        <v>728</v>
+      </c>
+      <c r="C163" t="s" s="2">
         <v>742</v>
-      </c>
-      <c r="B163" t="s" s="2">
-        <v>729</v>
-      </c>
-      <c r="C163" t="s" s="2">
-        <v>743</v>
       </c>
       <c r="D163" t="s" s="2">
         <v>81</v>
@@ -22061,14 +22054,14 @@
         <v>384</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="N163" s="2"/>
       <c r="O163" t="s" s="2">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="P163" t="s" s="2">
         <v>81</v>
@@ -22097,7 +22090,7 @@
       </c>
       <c r="Y163" s="2"/>
       <c r="Z163" t="s" s="2">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="AA163" t="s" s="2">
         <v>81</v>
@@ -22115,7 +22108,7 @@
         <v>81</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>79</v>
@@ -22130,7 +22123,7 @@
         <v>101</v>
       </c>
       <c r="AK163" t="s" s="2">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="AL163" t="s" s="2">
         <v>107</v>
@@ -22139,7 +22132,7 @@
         <v>81</v>
       </c>
       <c r="AN163" t="s" s="2">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="AO163" t="s" s="2">
         <v>81</v>
@@ -22147,10 +22140,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -22173,19 +22166,19 @@
         <v>81</v>
       </c>
       <c r="K164" t="s" s="2">
+        <v>746</v>
+      </c>
+      <c r="L164" t="s" s="2">
         <v>747</v>
       </c>
-      <c r="L164" t="s" s="2">
+      <c r="M164" t="s" s="2">
         <v>748</v>
       </c>
-      <c r="M164" t="s" s="2">
+      <c r="N164" t="s" s="2">
         <v>749</v>
       </c>
-      <c r="N164" t="s" s="2">
+      <c r="O164" t="s" s="2">
         <v>750</v>
-      </c>
-      <c r="O164" t="s" s="2">
-        <v>751</v>
       </c>
       <c r="P164" t="s" s="2">
         <v>81</v>
@@ -22234,7 +22227,7 @@
         <v>81</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>79</v>
@@ -22249,16 +22242,16 @@
         <v>101</v>
       </c>
       <c r="AK164" t="s" s="2">
+        <v>751</v>
+      </c>
+      <c r="AL164" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM164" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN164" t="s" s="2">
         <v>752</v>
-      </c>
-      <c r="AL164" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM164" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN164" t="s" s="2">
-        <v>753</v>
       </c>
       <c r="AO164" t="s" s="2">
         <v>81</v>
@@ -22266,10 +22259,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -22292,19 +22285,19 @@
         <v>81</v>
       </c>
       <c r="K165" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="L165" t="s" s="2">
         <v>643</v>
       </c>
-      <c r="L165" t="s" s="2">
+      <c r="M165" t="s" s="2">
         <v>644</v>
       </c>
-      <c r="M165" t="s" s="2">
-        <v>645</v>
-      </c>
       <c r="N165" t="s" s="2">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="O165" t="s" s="2">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="P165" t="s" s="2">
         <v>81</v>
@@ -22353,7 +22346,7 @@
         <v>81</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>79</v>
@@ -22365,19 +22358,19 @@
         <v>204</v>
       </c>
       <c r="AJ165" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="AK165" t="s" s="2">
         <v>648</v>
       </c>
-      <c r="AK165" t="s" s="2">
+      <c r="AL165" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM165" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN165" t="s" s="2">
         <v>649</v>
-      </c>
-      <c r="AL165" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM165" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN165" t="s" s="2">
-        <v>650</v>
       </c>
       <c r="AO165" t="s" s="2">
         <v>81</v>
@@ -22385,10 +22378,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22411,17 +22404,17 @@
         <v>81</v>
       </c>
       <c r="K166" t="s" s="2">
+        <v>756</v>
+      </c>
+      <c r="L166" t="s" s="2">
         <v>757</v>
       </c>
-      <c r="L166" t="s" s="2">
+      <c r="M166" t="s" s="2">
         <v>758</v>
-      </c>
-      <c r="M166" t="s" s="2">
-        <v>759</v>
       </c>
       <c r="N166" s="2"/>
       <c r="O166" t="s" s="2">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="P166" t="s" s="2">
         <v>81</v>
@@ -22470,7 +22463,7 @@
         <v>81</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>79</v>
@@ -22485,7 +22478,7 @@
         <v>101</v>
       </c>
       <c r="AK166" t="s" s="2">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="AL166" t="s" s="2">
         <v>107</v>
@@ -22494,7 +22487,7 @@
         <v>81</v>
       </c>
       <c r="AN166" t="s" s="2">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="AO166" t="s" s="2">
         <v>81</v>
@@ -22502,10 +22495,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -22531,14 +22524,14 @@
         <v>170</v>
       </c>
       <c r="L167" t="s" s="2">
+        <v>763</v>
+      </c>
+      <c r="M167" t="s" s="2">
         <v>764</v>
-      </c>
-      <c r="M167" t="s" s="2">
-        <v>765</v>
       </c>
       <c r="N167" s="2"/>
       <c r="O167" t="s" s="2">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="P167" t="s" s="2">
         <v>81</v>
@@ -22566,11 +22559,11 @@
         <v>260</v>
       </c>
       <c r="Y167" t="s" s="2">
+        <v>766</v>
+      </c>
+      <c r="Z167" t="s" s="2">
         <v>767</v>
       </c>
-      <c r="Z167" t="s" s="2">
-        <v>768</v>
-      </c>
       <c r="AA167" t="s" s="2">
         <v>81</v>
       </c>
@@ -22587,7 +22580,7 @@
         <v>81</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>79</v>
@@ -22602,7 +22595,7 @@
         <v>101</v>
       </c>
       <c r="AK167" t="s" s="2">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AL167" t="s" s="2">
         <v>107</v>
@@ -22611,7 +22604,7 @@
         <v>81</v>
       </c>
       <c r="AN167" t="s" s="2">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="AO167" t="s" s="2">
         <v>81</v>
@@ -22619,10 +22612,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -22648,14 +22641,14 @@
         <v>423</v>
       </c>
       <c r="L168" t="s" s="2">
+        <v>770</v>
+      </c>
+      <c r="M168" t="s" s="2">
         <v>771</v>
-      </c>
-      <c r="M168" t="s" s="2">
-        <v>772</v>
       </c>
       <c r="N168" s="2"/>
       <c r="O168" t="s" s="2">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="P168" t="s" s="2">
         <v>81</v>
@@ -22704,7 +22697,7 @@
         <v>81</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>79</v>
@@ -22713,13 +22706,13 @@
         <v>89</v>
       </c>
       <c r="AI168" t="s" s="2">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="AJ168" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK168" t="s" s="2">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="AL168" t="s" s="2">
         <v>107</v>
@@ -22728,7 +22721,7 @@
         <v>81</v>
       </c>
       <c r="AN168" t="s" s="2">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="AO168" t="s" s="2">
         <v>81</v>
@@ -22736,10 +22729,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -22765,10 +22758,10 @@
         <v>340</v>
       </c>
       <c r="L169" t="s" s="2">
+        <v>777</v>
+      </c>
+      <c r="M169" t="s" s="2">
         <v>778</v>
-      </c>
-      <c r="M169" t="s" s="2">
-        <v>779</v>
       </c>
       <c r="N169" s="2"/>
       <c r="O169" s="2"/>
@@ -22819,7 +22812,7 @@
         <v>81</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>79</v>
@@ -22834,7 +22827,7 @@
         <v>101</v>
       </c>
       <c r="AK169" t="s" s="2">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="AL169" t="s" s="2">
         <v>107</v>
@@ -22851,10 +22844,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -22877,19 +22870,19 @@
         <v>81</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="L170" t="s" s="2">
+        <v>781</v>
+      </c>
+      <c r="M170" t="s" s="2">
         <v>782</v>
       </c>
-      <c r="M170" t="s" s="2">
+      <c r="N170" t="s" s="2">
         <v>783</v>
       </c>
-      <c r="N170" t="s" s="2">
+      <c r="O170" t="s" s="2">
         <v>784</v>
-      </c>
-      <c r="O170" t="s" s="2">
-        <v>785</v>
       </c>
       <c r="P170" t="s" s="2">
         <v>81</v>
@@ -22938,7 +22931,7 @@
         <v>81</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>79</v>
@@ -22953,10 +22946,10 @@
         <v>101</v>
       </c>
       <c r="AK170" t="s" s="2">
+        <v>785</v>
+      </c>
+      <c r="AL170" t="s" s="2">
         <v>786</v>
-      </c>
-      <c r="AL170" t="s" s="2">
-        <v>787</v>
       </c>
       <c r="AM170" t="s" s="2">
         <v>81</v>
@@ -22970,10 +22963,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -23085,10 +23078,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -23202,14 +23195,14 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E173" s="2"/>
       <c r="F173" t="s" s="2">
@@ -23231,10 +23224,10 @@
         <v>110</v>
       </c>
       <c r="L173" t="s" s="2">
+        <v>725</v>
+      </c>
+      <c r="M173" t="s" s="2">
         <v>726</v>
-      </c>
-      <c r="M173" t="s" s="2">
-        <v>727</v>
       </c>
       <c r="N173" t="s" s="2">
         <v>113</v>
@@ -23289,7 +23282,7 @@
         <v>81</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>79</v>
@@ -23321,10 +23314,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -23350,16 +23343,16 @@
         <v>384</v>
       </c>
       <c r="L174" t="s" s="2">
+        <v>791</v>
+      </c>
+      <c r="M174" t="s" s="2">
         <v>792</v>
       </c>
-      <c r="M174" t="s" s="2">
+      <c r="N174" t="s" s="2">
         <v>793</v>
       </c>
-      <c r="N174" t="s" s="2">
+      <c r="O174" t="s" s="2">
         <v>794</v>
-      </c>
-      <c r="O174" t="s" s="2">
-        <v>795</v>
       </c>
       <c r="P174" t="s" s="2">
         <v>81</v>
@@ -23408,7 +23401,7 @@
         <v>81</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>89</v>
@@ -23423,16 +23416,16 @@
         <v>101</v>
       </c>
       <c r="AK174" t="s" s="2">
+        <v>795</v>
+      </c>
+      <c r="AL174" t="s" s="2">
         <v>796</v>
       </c>
-      <c r="AL174" t="s" s="2">
+      <c r="AM174" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN174" t="s" s="2">
         <v>797</v>
-      </c>
-      <c r="AM174" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN174" t="s" s="2">
-        <v>798</v>
       </c>
       <c r="AO174" t="s" s="2">
         <v>81</v>
@@ -23440,10 +23433,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -23469,16 +23462,16 @@
         <v>539</v>
       </c>
       <c r="L175" t="s" s="2">
+        <v>799</v>
+      </c>
+      <c r="M175" t="s" s="2">
         <v>800</v>
       </c>
-      <c r="M175" t="s" s="2">
+      <c r="N175" t="s" s="2">
         <v>801</v>
       </c>
-      <c r="N175" t="s" s="2">
+      <c r="O175" t="s" s="2">
         <v>802</v>
-      </c>
-      <c r="O175" t="s" s="2">
-        <v>803</v>
       </c>
       <c r="P175" t="s" s="2">
         <v>81</v>
@@ -23527,7 +23520,7 @@
         <v>81</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>79</v>
@@ -23542,16 +23535,16 @@
         <v>101</v>
       </c>
       <c r="AK175" t="s" s="2">
+        <v>803</v>
+      </c>
+      <c r="AL175" t="s" s="2">
         <v>804</v>
       </c>
-      <c r="AL175" t="s" s="2">
+      <c r="AM175" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN175" t="s" s="2">
         <v>805</v>
-      </c>
-      <c r="AM175" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN175" t="s" s="2">
-        <v>806</v>
       </c>
       <c r="AO175" t="s" s="2">
         <v>81</v>
@@ -23559,14 +23552,14 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="E176" s="2"/>
       <c r="F176" t="s" s="2">
@@ -23585,16 +23578,16 @@
         <v>81</v>
       </c>
       <c r="K176" t="s" s="2">
+        <v>808</v>
+      </c>
+      <c r="L176" t="s" s="2">
         <v>809</v>
       </c>
-      <c r="L176" t="s" s="2">
+      <c r="M176" t="s" s="2">
         <v>810</v>
       </c>
-      <c r="M176" t="s" s="2">
+      <c r="N176" t="s" s="2">
         <v>811</v>
-      </c>
-      <c r="N176" t="s" s="2">
-        <v>812</v>
       </c>
       <c r="O176" s="2"/>
       <c r="P176" t="s" s="2">
@@ -23644,7 +23637,7 @@
         <v>81</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>79</v>
@@ -23656,10 +23649,10 @@
         <v>81</v>
       </c>
       <c r="AJ176" t="s" s="2">
-        <v>813</v>
+        <v>101</v>
       </c>
       <c r="AK176" t="s" s="2">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="AL176" t="s" s="2">
         <v>107</v>
@@ -23668,7 +23661,7 @@
         <v>81</v>
       </c>
       <c r="AN176" t="s" s="2">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="AO176" t="s" s="2">
         <v>81</v>
@@ -23676,10 +23669,10 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -23702,19 +23695,19 @@
         <v>90</v>
       </c>
       <c r="K177" t="s" s="2">
+        <v>815</v>
+      </c>
+      <c r="L177" t="s" s="2">
+        <v>816</v>
+      </c>
+      <c r="M177" t="s" s="2">
         <v>817</v>
       </c>
-      <c r="L177" t="s" s="2">
+      <c r="N177" t="s" s="2">
         <v>818</v>
       </c>
-      <c r="M177" t="s" s="2">
+      <c r="O177" t="s" s="2">
         <v>819</v>
-      </c>
-      <c r="N177" t="s" s="2">
-        <v>820</v>
-      </c>
-      <c r="O177" t="s" s="2">
-        <v>821</v>
       </c>
       <c r="P177" t="s" s="2">
         <v>81</v>
@@ -23763,7 +23756,7 @@
         <v>81</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>79</v>
@@ -23778,10 +23771,10 @@
         <v>101</v>
       </c>
       <c r="AK177" t="s" s="2">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="AL177" t="s" s="2">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="AM177" t="s" s="2">
         <v>81</v>
@@ -23795,10 +23788,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -23821,19 +23814,19 @@
         <v>90</v>
       </c>
       <c r="K178" t="s" s="2">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="L178" t="s" s="2">
+        <v>822</v>
+      </c>
+      <c r="M178" t="s" s="2">
+        <v>823</v>
+      </c>
+      <c r="N178" t="s" s="2">
         <v>824</v>
       </c>
-      <c r="M178" t="s" s="2">
+      <c r="O178" t="s" s="2">
         <v>825</v>
-      </c>
-      <c r="N178" t="s" s="2">
-        <v>826</v>
-      </c>
-      <c r="O178" t="s" s="2">
-        <v>827</v>
       </c>
       <c r="P178" t="s" s="2">
         <v>81</v>
@@ -23882,7 +23875,7 @@
         <v>81</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>79</v>
@@ -23897,7 +23890,7 @@
         <v>101</v>
       </c>
       <c r="AK178" t="s" s="2">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="AL178" t="s" s="2">
         <v>107</v>
@@ -23914,10 +23907,10 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -24029,10 +24022,10 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -24146,14 +24139,14 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E181" s="2"/>
       <c r="F181" t="s" s="2">
@@ -24175,10 +24168,10 @@
         <v>110</v>
       </c>
       <c r="L181" t="s" s="2">
+        <v>725</v>
+      </c>
+      <c r="M181" t="s" s="2">
         <v>726</v>
-      </c>
-      <c r="M181" t="s" s="2">
-        <v>727</v>
       </c>
       <c r="N181" t="s" s="2">
         <v>113</v>
@@ -24233,7 +24226,7 @@
         <v>81</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>79</v>
@@ -24265,10 +24258,10 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -24291,16 +24284,16 @@
         <v>90</v>
       </c>
       <c r="K182" t="s" s="2">
+        <v>831</v>
+      </c>
+      <c r="L182" t="s" s="2">
+        <v>832</v>
+      </c>
+      <c r="M182" t="s" s="2">
         <v>833</v>
       </c>
-      <c r="L182" t="s" s="2">
+      <c r="N182" t="s" s="2">
         <v>834</v>
-      </c>
-      <c r="M182" t="s" s="2">
-        <v>835</v>
-      </c>
-      <c r="N182" t="s" s="2">
-        <v>836</v>
       </c>
       <c r="O182" s="2"/>
       <c r="P182" t="s" s="2">
@@ -24350,7 +24343,7 @@
         <v>81</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>89</v>
@@ -24374,7 +24367,7 @@
         <v>81</v>
       </c>
       <c r="AN182" t="s" s="2">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="AO182" t="s" s="2">
         <v>81</v>
@@ -24382,10 +24375,10 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -24411,10 +24404,10 @@
         <v>170</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="N183" s="2"/>
       <c r="O183" s="2"/>
@@ -24444,10 +24437,10 @@
         <v>260</v>
       </c>
       <c r="Y183" t="s" s="2">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="Z183" t="s" s="2">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="AA183" t="s" s="2">
         <v>81</v>
@@ -24465,7 +24458,7 @@
         <v>81</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>89</v>
@@ -24480,7 +24473,7 @@
         <v>101</v>
       </c>
       <c r="AK183" t="s" s="2">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="AL183" t="s" s="2">
         <v>107</v>

--- a/main/ig/StructureDefinition-fr-patient-ins-document.xlsx
+++ b/main/ig/StructureDefinition-fr-patient-ins-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-21T15:23:03+00:00</t>
+    <t>2025-10-21T16:49:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-patient-ins-document.xlsx
+++ b/main/ig/StructureDefinition-fr-patient-ins-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-21T16:49:23+00:00</t>
+    <t>2025-10-21T17:18:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-patient-ins-document.xlsx
+++ b/main/ig/StructureDefinition-fr-patient-ins-document.xlsx
@@ -39,13 +39,13 @@
     <t>Name</t>
   </si>
   <si>
-    <t>FrPatientINSDocument</t>
+    <t>FRPatientINSDocument</t>
   </si>
   <si>
     <t>Title</t>
   </si>
   <si>
-    <t>Fr Patient INS Document</t>
+    <t>FR Patient INS Document</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-21T17:18:21+00:00</t>
+    <t>2025-10-22T08:56:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
